--- a/Outputs/Scenarios/PtX_demand_IT_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_IT_Electrification.xlsx
@@ -1555,7 +1555,7 @@
         <v>0.006209912877846326</v>
       </c>
       <c r="K30" t="n">
-        <v>0.08280046734176597</v>
+        <v>0.08280046734176595</v>
       </c>
     </row>
     <row r="31">
@@ -1583,7 +1583,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.225069234162998e-08</v>
+        <v>1.225069234162997e-08</v>
       </c>
       <c r="I31" t="n">
         <v>0.0172509089954226</v>
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.08280046734176597</v>
+        <v>0.08280046734176595</v>
       </c>
     </row>
     <row r="34">
@@ -1975,7 +1975,7 @@
         <v>2050</v>
       </c>
       <c r="C42" t="n">
-        <v>0.006846551871567273</v>
+        <v>0.006846551871567274</v>
       </c>
       <c r="D42" t="n">
         <v>0.00189924469545543</v>

--- a/Outputs/Scenarios/PtX_demand_IT_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_IT_Electrification.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.004194814982415169</v>
       </c>
       <c r="K16" t="n">
-        <v>0.01418092555773339</v>
+        <v>0.0169556770774016</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.002363487592955566</v>
+        <v>0.002945175385740022</v>
       </c>
     </row>
     <row r="18">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.009453950371822263</v>
+        <v>0.01178070154296009</v>
       </c>
     </row>
     <row r="19">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.01418092555773339</v>
+        <v>0.01178070154296009</v>
       </c>
     </row>
     <row r="20">
@@ -1333,7 +1333,7 @@
         <v>0.0003361732549850976</v>
       </c>
       <c r="K24" t="n">
-        <v>0.02039210654845916</v>
+        <v>0.02002010247659739</v>
       </c>
     </row>
     <row r="25">
@@ -1370,7 +1370,7 @@
         <v>0.002034857419672514</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1914562237161125</v>
+        <v>0.1879635735263726</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>6.044018326571965e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.002363487592955566</v>
+        <v>0.002945175385740022</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.006209912877846326</v>
       </c>
       <c r="K30" t="n">
-        <v>0.08280046734176595</v>
+        <v>0.09075731781472617</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.01380007789029433</v>
+        <v>0.01576440842105717</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.05520031156117731</v>
+        <v>0.06305763368422869</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.08280046734176595</v>
+        <v>0.06305763368422869</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0.0003268375198866488</v>
       </c>
       <c r="K42" t="n">
-        <v>0.01380007789029433</v>
+        <v>0.01576440842105717</v>
       </c>
     </row>
     <row r="43">
